--- a/examples/status-machine/本期岗位.xlsx
+++ b/examples/status-machine/本期岗位.xlsx
@@ -441,13 +441,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +473,16 @@
           <t>状态-会议</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>拟任人</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>流程节点</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -489,6 +501,8 @@
           <t>01-新增</t>
         </is>
       </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -507,6 +521,8 @@
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -529,6 +545,16 @@
           <t>01-新增</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>部门评审</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -547,6 +573,8 @@
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -561,6 +589,8 @@
       </c>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -583,6 +613,100 @@
           <t>02-进展更新</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>运营部-总监</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>公司审批</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>P008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>行政部-经理</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>02-进展更新</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>周七</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>公司审批</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>P009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>质量部-部长</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>变动通报</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>01-新增</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/status-machine/本期岗位.xlsx
+++ b/examples/status-machine/本期岗位.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -71,10 +72,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,11 +446,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
